--- a/raid-agency-app/public/templates/related-objects-template.xlsx
+++ b/raid-agency-app/public/templates/related-objects-template.xlsx
@@ -132,7 +132,7 @@
     <t>Do not delete the rows labelled "Import table starts here" and "Import table ends here"</t>
   </si>
   <si>
-    <t>Identifier must be the full URL of one of the types supported by RAiD. For example, a DOI would look like https://doi.org/10.0001/01238</t>
+    <t>Identifier must be the full URL of a DOI, Handle, RRID, ARK, or Web Archive snapshot. For example, a DOI would look like https://doi.org/10.0001/01238</t>
   </si>
   <si>
     <t>Use the Excel drop-down lists to avoid typos</t>

--- a/raid-agency-app/public/templates/related-objects-template.xlsx
+++ b/raid-agency-app/public/templates/related-objects-template.xlsx
@@ -132,7 +132,7 @@
     <t>Do not delete the rows labelled "Import table starts here" and "Import table ends here"</t>
   </si>
   <si>
-    <t>Identifier must be the full URL of a DOI, Handle, RRID, ARK, or Web Archive snapshot. For example, a DOI would look like https://doi.org/10.0001/01238</t>
+    <t>Identifier must be the full URL of a DOI, Handle, RRID, or Web Archive snapshot. For example, a DOI would look like https://doi.org/10.0001/01238</t>
   </si>
   <si>
     <t>Use the Excel drop-down lists to avoid typos</t>
